--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.33744433427053</v>
+        <v>13.21733470431896</v>
       </c>
       <c r="D2" t="n">
-        <v>81.72724618118887</v>
+        <v>13.28067750444319</v>
       </c>
       <c r="E2" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F2" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>88.54177983752803</v>
+        <v>14.38803922359831</v>
       </c>
       <c r="D3" t="n">
-        <v>88.89683936200885</v>
+        <v>14.44573639632644</v>
       </c>
       <c r="E3" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F3" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.92527890718945</v>
+        <v>12.82535782241829</v>
       </c>
       <c r="D4" t="n">
-        <v>79.29295340096625</v>
+        <v>12.88510492765702</v>
       </c>
       <c r="E4" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F4" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.94475184126661</v>
+        <v>10.87852217420583</v>
       </c>
       <c r="D5" t="n">
-        <v>67.33638236125407</v>
+        <v>10.94216213370379</v>
       </c>
       <c r="E5" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F5" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.72844209505826</v>
+        <v>8.405871840446967</v>
       </c>
       <c r="D6" t="n">
-        <v>52.12943328693942</v>
+        <v>8.471032909127656</v>
       </c>
       <c r="E6" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F6" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.71809868627568</v>
+        <v>10.3541910365198</v>
       </c>
       <c r="D7" t="n">
-        <v>64.05866528526317</v>
+        <v>10.40953310885527</v>
       </c>
       <c r="E7" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F7" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.63221910030136</v>
+        <v>7.415235603798971</v>
       </c>
       <c r="D8" t="n">
-        <v>46.01532206035426</v>
+        <v>7.477489834807568</v>
       </c>
       <c r="E8" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F8" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>61.42545526040592</v>
+        <v>9.981636479815963</v>
       </c>
       <c r="D9" t="n">
-        <v>61.7234248269959</v>
+        <v>10.03005653438684</v>
       </c>
       <c r="E9" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F9" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.91600293524679</v>
+        <v>5.673850476977604</v>
       </c>
       <c r="D10" t="n">
-        <v>35.27641807122787</v>
+        <v>5.73241793657453</v>
       </c>
       <c r="E10" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F10" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.48973241807311</v>
+        <v>8.529581517936881</v>
       </c>
       <c r="D11" t="n">
-        <v>52.77259527275744</v>
+        <v>8.575546731823083</v>
       </c>
       <c r="E11" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F11" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.75799115769177</v>
+        <v>4.998173563124912</v>
       </c>
       <c r="D12" t="n">
-        <v>31.15324756599352</v>
+        <v>5.062402729473947</v>
       </c>
       <c r="E12" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F12" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.72874551941134</v>
+        <v>4.993421146904343</v>
       </c>
       <c r="D13" t="n">
-        <v>31.03478133827863</v>
+        <v>5.043151967470278</v>
       </c>
       <c r="E13" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F13" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.30013283763388</v>
+        <v>1.673771586115505</v>
       </c>
       <c r="D14" t="n">
-        <v>10.52087662464452</v>
+        <v>1.709642451504734</v>
       </c>
       <c r="E14" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F14" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.33503307257054</v>
+        <v>7.204442874292713</v>
       </c>
       <c r="D15" t="n">
-        <v>44.30892797278106</v>
+        <v>7.200200795576922</v>
       </c>
       <c r="E15" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F15" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.54086231809144</v>
+        <v>2.687890126689859</v>
       </c>
       <c r="D16" t="n">
-        <v>16.54072821012267</v>
+        <v>2.687868334144933</v>
       </c>
       <c r="E16" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F16" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.34256409196976</v>
+        <v>6.393166664945086</v>
       </c>
       <c r="D17" t="n">
-        <v>39.41264584032483</v>
+        <v>6.404554949052786</v>
       </c>
       <c r="E17" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F17" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.92528681437503</v>
+        <v>6.162859107335942</v>
       </c>
       <c r="D18" t="n">
-        <v>37.85920761371141</v>
+        <v>6.152121237228105</v>
       </c>
       <c r="E18" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F18" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.66398049792986</v>
+        <v>5.957896830913602</v>
       </c>
       <c r="D19" t="n">
-        <v>36.53396648837305</v>
+        <v>5.93676955436062</v>
       </c>
       <c r="E19" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F19" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.18436032078043</v>
+        <v>3.76745855212682</v>
       </c>
       <c r="D20" t="n">
-        <v>22.85387409912775</v>
+        <v>3.71375454110826</v>
       </c>
       <c r="E20" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F20" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>45.95236948137826</v>
+        <v>7.467260040723967</v>
       </c>
       <c r="D21" t="n">
-        <v>45.68011576411517</v>
+        <v>7.423018811668715</v>
       </c>
       <c r="E21" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F21" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>38.38841871790501</v>
+        <v>6.238118041659565</v>
       </c>
       <c r="D22" t="n">
-        <v>38.11677789963526</v>
+        <v>6.19397640869073</v>
       </c>
       <c r="E22" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F22" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>33.83952441209082</v>
+        <v>5.498922716964759</v>
       </c>
       <c r="D23" t="n">
-        <v>33.43950357536359</v>
+        <v>5.433919330996583</v>
       </c>
       <c r="E23" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F23" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>38.52412666239822</v>
+        <v>6.26017058263971</v>
       </c>
       <c r="D24" t="n">
-        <v>38.15981363545099</v>
+        <v>6.200969715760787</v>
       </c>
       <c r="E24" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F24" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>60.03573454646855</v>
+        <v>9.755806863801141</v>
       </c>
       <c r="D25" t="n">
-        <v>59.74754427601731</v>
+        <v>9.708975944852813</v>
       </c>
       <c r="E25" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F25" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>45.74897532128501</v>
+        <v>7.434208489708814</v>
       </c>
       <c r="D26" t="n">
-        <v>45.38350971852109</v>
+        <v>7.374820329259677</v>
       </c>
       <c r="E26" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F26" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>51.22317444856822</v>
+        <v>8.323765847892336</v>
       </c>
       <c r="D27" t="n">
-        <v>50.86528133112935</v>
+        <v>8.26560821630852</v>
       </c>
       <c r="E27" t="n">
-        <v>18.74766875211015</v>
+        <v>3.046496172217899</v>
       </c>
       <c r="F27" t="n">
-        <v>18.85873062193147</v>
+        <v>3.064543726063865</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
